--- a/reports/thaura-bug-report.xlsx
+++ b/reports/thaura-bug-report.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
@@ -747,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -910,12 +910,12 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>The assistant does not falsely claim persistence - it states the limitation up front. A separate, genuine automatic memory subsystem exists (Account -&gt; Memory, backed by GET /api/memories) but had not captured anything after our short synthetic test conversations.</t>
+          <t>The assistant does not falsely claim persistence - it states the limitation up front. A separate, genuine automatic memory subsystem exists (Account -&gt; Memory, backed by GET /api/memories); it had not captured anything after our short synthetic test conversations, but was subsequently confirmed working (2026-09-16) when the tester shared a real CV in genuine usage - the store populated with substantive content, phrased oddly as a second-person instruction rather than a neutral summary.</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>discovery-evidence/memory-incognito-test/full-test-results.json, memory-settings-network-log.json</t>
+          <t>discovery-evidence/memory-incognito-test/full-test-results.json, memory-settings-network-log.json, memory-panel-cv-capture.json</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,66 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>This describes the extraction pipeline's documented behavior, not a failure - whether the assistant can still read image-embedded text via multimodal vision at chat-turn time was not independently re-verified this session (see Not Tested).</t>
+          <t>This describes the extraction pipeline's documented behavior, not a failure - re-verified 2026-09-16 that the assistant can still read image-embedded text via multimodal vision at chat-turn time (asked to quote text from sample.png, correctly replied with the exact baked-in marker QA-IMG-MARKER-30457), so end-user-visible functionality is unaffected.</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>discovery-evidence/upload-test/extraction-verification.json</t>
+          <t>discovery-evidence/upload-test/extraction-verification.json, image-ocr-verification.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>OBS-009</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Developer API</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>The documented 8-concurrent-requests-per-key rate limit did not trigger: 9 genuinely concurrent requests (fired via Promise.all, each in-flight ~570-630ms, confirmed non-overlapping with the separately-tested 60/min window) all returned 402 insufficient_balance, none returned 429. The documented 60-requests/minute limit, by contrast, was confirmed exactly - requests 1-60 reached the billing gate, 61-65 were correctly rejected with 429.</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Not a security risk - a laxer-than-documented concurrency limit is permissive, not exploitable, and no abuse was demonstrated. This is a discrepancy between the published API contract at thaura.ai/api-platform and observed behavior, flagged for docs/product review rather than as a defect. Only 9 concurrent requests were tried once, to stay within a single safe probe rather than approaching anything resembling load-testing production.</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>discovery-evidence/api-test/rate-limit-test-results.json, concurrency-test-isolated-results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>OBS-010</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Settings/Account UI</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>The Settings 'Name' field enforces a genuine maxlength=80 attribute (confirmed by direct attribute inspection), but an 80-character unbroken name overflows the "Happy Wednesday, {name}" greeting header and the sidebar profile label - neither has truncation/ellipsis handling for a name at that length.</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Length validation itself works correctly (not a data-integrity issue); this is a display/layout polish gap for an edge case (a real name is unlikely to be 80 characters with no spaces). Blank-name submission is correctly blocked (Save button disabled), and a script/HTML injection payload in the same field was fully sanitized with no XSS - both PASS.</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>discovery-evidence/settings-negative-test/results.json, field-attributes-and-email-check.json, 02-long-name-after-save.png</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1223,51 +1277,51 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Image-embedded text readability by the assistant in a live chat turn</t>
+          <t>API: temperature boundary enforcement</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>File Upload</t>
+          <t>API</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Deprioritized under a hard 5-message/5-hour free-tier budget in favor of higher-value memory/incognito/file-isolation tests. The upload-time extraction pipeline behavior (no OCR, opaque "Image file" placeholder) is documented, but whether the model can still read image text via multimodal vision when asked directly was not independently re-confirmed this session.</t>
+          <t>Billing-gated - the zero-balance account receives 402 insufficient_balance before any temperature validation/execution logic can run. Funding was evaluated and not recommended (see API Funding Decision).</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>discovery-evidence/upload-test/extraction-verification.json</t>
+          <t>discovery-evidence/api-test/validation-batch-results.json (API-10 to API-13)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Cross-account file isolation (two distinct real accounts)</t>
+          <t>API: max_tokens / max_completion_tokens behavior and 32000 cap</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>File Upload / Isolation</t>
+          <t>API</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Assessment scope explicitly excludes using another real person's account. Same-account cross-conversation isolation and direct-file-ID access (401/404) were tested instead as the closest safe proxy.</t>
+          <t>Billing-gated, same reason as above.</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>discovery-evidence/upload-test/isolation-probe-results.json, memory-incognito-test/full-test-results.json</t>
+          <t>discovery-evidence/api-test/validation-batch-results.json (API-14, API-15, API-15b)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>API: temperature boundary enforcement</t>
+          <t>API: max_tokens vs max_completion_tokens precedence</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -1277,19 +1331,19 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Billing-gated - the zero-balance account receives 402 insufficient_balance before any temperature validation/execution logic can run. Funding was evaluated and not recommended (see API Funding Decision).</t>
+          <t>Billing-gated, same reason as above.</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>discovery-evidence/api-test/validation-batch-results.json (API-10 to API-13)</t>
+          <t>discovery-evidence/api-test/validation-batch-results.json (API-17)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>API: max_tokens / max_completion_tokens behavior and 32000 cap</t>
+          <t>API: ignored/pass-through parameters (top_p, frequency_penalty, presence_penalty, n, user)</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -1299,19 +1353,19 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Billing-gated, same reason as above.</t>
+          <t>Billing-gated, same reason as above - parameters are accepted at the structural-validation layer, but their effect on generation cannot be observed without a funded call.</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>discovery-evidence/api-test/validation-batch-results.json (API-14, API-15, API-15b)</t>
+          <t>discovery-evidence/api-test/validation-batch-results.json (API-20)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>API: max_tokens vs max_completion_tokens precedence</t>
+          <t>API: tools / tool_choice function-calling behavior</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -1326,14 +1380,14 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>discovery-evidence/api-test/validation-batch-results.json (API-17)</t>
+          <t>discovery-evidence/api-test/validation-batch-results.json (API-21)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>API: ignored/pass-through parameters (top_p, frequency_penalty, presence_penalty, n, user)</t>
+          <t>API: streaming vs non-streaming response shape</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -1343,19 +1397,19 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Billing-gated, same reason as above - parameters are accepted at the structural-validation layer, but their effect on generation cannot be observed without a funded call.</t>
+          <t>Billing-gated - not reachable without a successful (funded) generation call.</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>discovery-evidence/api-test/validation-batch-results.json (API-20)</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>API: tools / tool_choice function-calling behavior</t>
+          <t>API: usage accounting (token counts / cost reporting)</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -1370,14 +1424,14 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>discovery-evidence/api-test/validation-batch-results.json (API-21)</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>API: streaming vs non-streaming response shape</t>
+          <t>API: rate/concurrency limits</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -1387,7 +1441,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Billing-gated - not reachable without a successful (funded) generation call.</t>
+          <t>Would require multiple funded, near-simultaneous calls to observe meaningfully; not attempted, both due to lack of balance and to avoid any appearance of a DoS-style probe against production infrastructure.</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -1399,64 +1453,20 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>API: usage accounting (token counts / cost reporting)</t>
+          <t>Incognito behavior specifically under a mid-session refresh</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>Incognito</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Billing-gated, same reason as above.</t>
+          <t>Not directly re-exercised this session under the quota budget; the URL-scoping evidence (no persistent ?chatId= while incognito) strongly implies a refresh would lose the conversation, consistent with "not saved", but this exact scenario was not run.</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>API: rate/concurrency limits</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Would require multiple funded, near-simultaneous calls to observe meaningfully; not attempted, both due to lack of balance and to avoid any appearance of a DoS-style probe against production infrastructure.</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Incognito behavior specifically under a mid-session refresh</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Incognito</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Not directly re-exercised this session under the quota budget; the URL-scoping evidence (no persistent ?chatId= while incognito) strongly implies a refresh would lose the conversation, consistent with "not saved", but this exact scenario was not run.</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>discovery-evidence/memory-incognito-test/incognito-verified-results.json</t>
         </is>
